--- a/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor</t>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 10,81</t>
+          <t>0,89; 11,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,41</t>
+          <t>0,47; 5,04</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,95</t>
+          <t>0,4; 2,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,43</t>
+          <t>1,23; 3,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,48</t>
+          <t>0,99; 2,48</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,49</t>
+          <t>0,8; 6,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,78</t>
+          <t>0,52; 2,91</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,72</t>
+          <t>0,89; 2,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,57</t>
+          <t>0,9; 2,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,26</t>
+          <t>1,03; 2,21</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>485; 6121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>546; 5875</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11025</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15728</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1858; 9889</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6356; 18572</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9632; 24247</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3701</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4539</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1192; 9118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4330</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1721; 9656</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5908; 16993</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6848; 19006</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14698; 31461</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 11,19</t>
+          <t>0,96; 10,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,04</t>
+          <t>0,45; 4,95</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,15</t>
+          <t>0,43; 2,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,59</t>
+          <t>1,23; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,48</t>
+          <t>0,99; 2,42</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,1</t>
+          <t>0,87; 5,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,91</t>
+          <t>0,52; 2,97</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,56</t>
+          <t>0,9; 2,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,5</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,21</t>
+          <t>1,09; 2,19</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>485; 6121</t>
+          <t>527; 5699</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>546; 5875</t>
+          <t>528; 5776</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1858; 9889</t>
+          <t>1964; 9901</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6356; 18572</t>
+          <t>6336; 19494</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9632; 24247</t>
+          <t>9697; 23672</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1192; 9118</t>
+          <t>1303; 8817</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4330</t>
+          <t>0; 4558</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1721; 9656</t>
+          <t>1735; 9869</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5908; 16993</t>
+          <t>5993; 16857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6848; 19006</t>
+          <t>6812; 19822</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14698; 31461</t>
+          <t>15582; 31232</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,47; 10,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,95</t>
+          <t>0,62; 5,2</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,15</t>
+          <t>1,22; 3,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,77</t>
+          <t>0,43; 2,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,42</t>
+          <t>1,07; 2,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,9</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,94; 5,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,97</t>
+          <t>0,62; 3,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,54</t>
+          <t>0,92; 2,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>1,01; 2,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,19</t>
+          <t>1,14; 2,39</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2011</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>527; 5699</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>689; 4988</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>528; 5776</t>
+          <t>641; 5382</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15246</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1964; 9901</t>
+          <t>5784; 16988</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6336; 19494</t>
+          <t>1857; 9350</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9697; 23672</t>
+          <t>9687; 23700</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>876</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4679</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1303; 8817</t>
+          <t>0; 4431</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4558</t>
+          <t>1403; 8631</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1735; 9869</t>
+          <t>1960; 9634</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5993; 16857</t>
+          <t>6463; 19047</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6812; 19822</t>
+          <t>6373; 18149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15582; 31232</t>
+          <t>15148; 31781</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 10,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 5,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 3,57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,43; 2,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,07; 2,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,64</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,94; 5,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 3,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 2,72</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,01; 2,89</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 2,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.043006007245722</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.01943048772637171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.01473811751763276</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.006196709222819103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>689; 4988</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>641; 5382</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0.1066859622412313</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.05200752832506462</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.02212010327148472</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01094411766551336</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01680357994670116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10522</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4724</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15246</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01216016778751223</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.004302881007426578</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01067663825028498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5784; 16988</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1857; 9350</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9687; 23700</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03571263578332594</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02166311883389863</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02612226561915246</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.0052194226790305</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.02535850257542049</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01472172217303866</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.009357555852487242</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.006167677612637657</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4431</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1403; 8631</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1960; 9634</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.02639340636761676</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.05755034771309674</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03031023478525746</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01627647939490868</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01677055272274455</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01651013687533191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11398</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10538</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21936</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.009228946470148621</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01014259684157659</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01140138861046169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6463; 19047</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>6373; 18149</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15148; 31781</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02719846505330167</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02888491655583849</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02391991309193495</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>689</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>4988</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>5382</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10522</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>4724</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>15246</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5784</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1857</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>9687</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>16988</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>9350</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>23700</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>876</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3803</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4431</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8631</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9634</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11398</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>10538</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>21936</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>6373</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>15148</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>19047</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>18149</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>31781</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>